--- a/crdo/dist/20261025_Credo模型_v0.2.1.xlsx
+++ b/crdo/dist/20261025_Credo模型_v0.2.1.xlsx
@@ -6836,7 +6836,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7073,7 +7073,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7194,7 +7194,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7315,7 +7315,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7436,7 +7436,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7557,7 +7557,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
